--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.17.1</t>
+    <t>2.18.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.18.0</t>
+    <t>2.19.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.19.1</t>
+    <t>2.19.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.19.3</t>
+    <t>2.19.4</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="166">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.19.4</t>
+    <t>2.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -436,6 +436,31 @@
   </si>
   <si>
     <t>Limit response of Patient to match given CPR.</t>
+  </si>
+  <si>
+    <t>plan-definition-action-display-order</t>
+  </si>
+  <si>
+    <t>https://kip.rkkp.dk/fhir/StructureDefinition/plan-definition-action-display-order</t>
+  </si>
+  <si>
+    <t>PlanDefinitionActionDisplayOrder</t>
+  </si>
+  <si>
+    <t>Display Order for PlanDefinition Action</t>
+  </si>
+  <si>
+    <t>2026-03-24T00:00:00+02:00</t>
+  </si>
+  <si>
+    <t>Specifies the desired display order of a PlanDefinition action (e.g. Questionnaire references). Lower values are displayed first.</t>
+  </si>
+  <si>
+    <t>element:PlanDefinition.action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
   </si>
   <si>
     <t>questionnaire-response-reference</t>
@@ -629,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B264"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1893,7 +1918,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>131</v>
+        <v>142</v>
       </c>
     </row>
     <row r="164">
@@ -1925,7 +1950,7 @@
         <v>23</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="168">
@@ -1993,7 +2018,7 @@
         <v>39</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>40</v>
+        <v>144</v>
       </c>
     </row>
     <row r="177">
@@ -2009,7 +2034,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="179">
@@ -2017,7 +2042,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="180">
@@ -2033,7 +2058,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="182">
@@ -2041,7 +2066,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="183">
@@ -2095,7 +2120,7 @@
         <v>23</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="190">
@@ -2179,7 +2204,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="201">
@@ -2187,7 +2212,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="202">
@@ -2203,7 +2228,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="204">
@@ -2211,7 +2236,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="205">
@@ -2265,7 +2290,7 @@
         <v>23</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="212">
@@ -2349,7 +2374,7 @@
         <v>2</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="223">
@@ -2357,7 +2382,7 @@
         <v>4</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="224">
@@ -2373,7 +2398,7 @@
         <v>8</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="226">
@@ -2381,7 +2406,7 @@
         <v>10</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="227">
@@ -2435,7 +2460,7 @@
         <v>23</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="234">
@@ -2503,6 +2528,176 @@
         <v>39</v>
       </c>
       <c r="B242" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B243" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B250" s="2"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B256" s="2"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B257" s="2"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B264" t="s" s="2">
         <v>40</v>
       </c>
     </row>
@@ -2513,7 +2708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK56"/>
+  <dimension ref="A1:AK61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.04296875" customWidth="true" bestFit="true"/>
@@ -6322,7 +6517,7 @@
         <v>141</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -6730,7 +6925,7 @@
         <v>22</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>102</v>
@@ -6804,7 +6999,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>32</v>
@@ -6836,10 +7031,10 @@
         <v>79</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -6907,7 +7102,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>82</v>
@@ -7010,7 +7205,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>88</v>
@@ -7113,7 +7308,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>95</v>
@@ -7159,7 +7354,7 @@
       </c>
       <c r="R45" s="2"/>
       <c r="S45" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>22</v>
@@ -7218,7 +7413,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>100</v>
@@ -7321,7 +7516,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>32</v>
@@ -7353,10 +7548,10 @@
         <v>79</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -7424,7 +7619,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>82</v>
@@ -7527,7 +7722,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>88</v>
@@ -7630,7 +7825,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>95</v>
@@ -7676,7 +7871,7 @@
       </c>
       <c r="R50" s="2"/>
       <c r="S50" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>22</v>
@@ -7735,7 +7930,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>100</v>
@@ -7838,7 +8033,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>32</v>
@@ -7870,10 +8065,10 @@
         <v>79</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -7941,7 +8136,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>82</v>
@@ -8044,7 +8239,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>88</v>
@@ -8147,7 +8342,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>95</v>
@@ -8193,7 +8388,7 @@
       </c>
       <c r="R55" s="2"/>
       <c r="S55" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>22</v>
@@ -8252,7 +8447,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>100</v>
@@ -8350,6 +8545,523 @@
         <v>22</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R57" s="2"/>
+      <c r="S57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R58" s="2"/>
+      <c r="S58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R59" s="2"/>
+      <c r="S59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="P60" s="2"/>
+      <c r="Q60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R60" s="2"/>
+      <c r="S60" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D61" s="2"/>
+      <c r="E61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R61" s="2"/>
+      <c r="S61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK61" t="s" s="2">
         <v>104</v>
       </c>
     </row>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.21.0</t>
+    <t>2.23.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.0</t>
+    <t>2.23.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.1</t>
+    <t>2.23.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="172">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.2</t>
+    <t>2.23.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -403,6 +403,24 @@
   </si>
   <si>
     <t>Limit responses of CarePlan to match the author of the given SOR-code.</t>
+  </si>
+  <si>
+    <t>VSLatest</t>
+  </si>
+  <si>
+    <t>https://kip.rkkp.dk/fhir/StructureDefinition/VSLatest</t>
+  </si>
+  <si>
+    <t>SearchParameterValueSetLatest</t>
+  </si>
+  <si>
+    <t>Search Parameter - Latest for ValueSets</t>
+  </si>
+  <si>
+    <t>2026-07-09T00:00:00+02:00</t>
+  </si>
+  <si>
+    <t>Limit response of ValueSets to match given Latest.</t>
   </si>
   <si>
     <t>access-sor-code</t>
@@ -654,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B286"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1748,7 +1766,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="142">
@@ -1780,7 +1798,7 @@
         <v>23</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="146">
@@ -1864,7 +1882,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="157">
@@ -1872,7 +1890,7 @@
         <v>4</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="158">
@@ -1888,7 +1906,7 @@
         <v>8</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="160">
@@ -1896,7 +1914,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="161">
@@ -1918,7 +1936,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="164">
@@ -2018,7 +2036,7 @@
         <v>39</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>144</v>
+        <v>40</v>
       </c>
     </row>
     <row r="177">
@@ -2034,7 +2052,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="179">
@@ -2042,7 +2060,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="180">
@@ -2058,7 +2076,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="182">
@@ -2066,7 +2084,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="183">
@@ -2088,7 +2106,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="186">
@@ -2120,7 +2138,7 @@
         <v>23</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="190">
@@ -2188,7 +2206,7 @@
         <v>39</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="199">
@@ -2204,7 +2222,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="201">
@@ -2212,7 +2230,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="202">
@@ -2228,7 +2246,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="204">
@@ -2236,7 +2254,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="205">
@@ -2258,7 +2276,7 @@
         <v>15</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="208">
@@ -2290,7 +2308,7 @@
         <v>23</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="212">
@@ -2374,7 +2392,7 @@
         <v>2</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="223">
@@ -2382,7 +2400,7 @@
         <v>4</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="224">
@@ -2398,7 +2416,7 @@
         <v>8</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="226">
@@ -2406,7 +2424,7 @@
         <v>10</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="227">
@@ -2428,7 +2446,7 @@
         <v>15</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="230">
@@ -2460,7 +2478,7 @@
         <v>23</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="234">
@@ -2544,7 +2562,7 @@
         <v>2</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="245">
@@ -2552,7 +2570,7 @@
         <v>4</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="246">
@@ -2568,7 +2586,7 @@
         <v>8</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="248">
@@ -2576,7 +2594,7 @@
         <v>10</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="249">
@@ -2598,7 +2616,7 @@
         <v>15</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="252">
@@ -2630,7 +2648,7 @@
         <v>23</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="256">
@@ -2698,6 +2716,176 @@
         <v>39</v>
       </c>
       <c r="B264" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B265" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B272" s="2"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B278" s="2"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B279" s="2"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B280" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B286" t="s" s="2">
         <v>40</v>
       </c>
     </row>
@@ -2708,7 +2896,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK61"/>
+  <dimension ref="A1:AK66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.04296875" customWidth="true" bestFit="true"/>
@@ -5891,7 +6079,7 @@
         <v>22</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>102</v>
@@ -6000,7 +6188,7 @@
         <v>136</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -6482,7 +6670,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>32</v>
@@ -6514,7 +6702,7 @@
         <v>79</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>143</v>
@@ -6585,7 +6773,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>82</v>
@@ -6688,7 +6876,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>88</v>
@@ -6791,7 +6979,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>95</v>
@@ -6837,7 +7025,7 @@
       </c>
       <c r="R40" s="2"/>
       <c r="S40" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>22</v>
@@ -6896,7 +7084,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>100</v>
@@ -6925,7 +7113,7 @@
         <v>22</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="M41" t="s" s="2">
         <v>102</v>
@@ -6999,7 +7187,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>32</v>
@@ -7031,10 +7219,10 @@
         <v>79</v>
       </c>
       <c r="M42" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -7102,7 +7290,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>82</v>
@@ -7205,7 +7393,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>88</v>
@@ -7308,7 +7496,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>95</v>
@@ -7354,7 +7542,7 @@
       </c>
       <c r="R45" s="2"/>
       <c r="S45" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>22</v>
@@ -7413,7 +7601,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>100</v>
@@ -7442,7 +7630,7 @@
         <v>22</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>102</v>
@@ -7516,7 +7704,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>32</v>
@@ -7548,10 +7736,10 @@
         <v>79</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -7619,7 +7807,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>82</v>
@@ -7722,7 +7910,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>88</v>
@@ -7825,7 +8013,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>95</v>
@@ -7871,7 +8059,7 @@
       </c>
       <c r="R50" s="2"/>
       <c r="S50" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>22</v>
@@ -7930,7 +8118,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>100</v>
@@ -8033,7 +8221,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>32</v>
@@ -8065,10 +8253,10 @@
         <v>79</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -8136,7 +8324,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>82</v>
@@ -8239,7 +8427,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>88</v>
@@ -8342,7 +8530,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>95</v>
@@ -8388,7 +8576,7 @@
       </c>
       <c r="R55" s="2"/>
       <c r="S55" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>22</v>
@@ -8447,7 +8635,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>100</v>
@@ -8550,7 +8738,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>32</v>
@@ -8582,10 +8770,10 @@
         <v>79</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" s="2"/>
@@ -8653,7 +8841,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>82</v>
@@ -8756,7 +8944,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>88</v>
@@ -8859,7 +9047,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>95</v>
@@ -8905,7 +9093,7 @@
       </c>
       <c r="R60" s="2"/>
       <c r="S60" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>22</v>
@@ -8964,7 +9152,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>100</v>
@@ -9062,6 +9250,523 @@
         <v>22</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D62" s="2"/>
+      <c r="E62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R62" s="2"/>
+      <c r="S62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="D63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R63" s="2"/>
+      <c r="S63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="D64" s="2"/>
+      <c r="E64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R64" s="2"/>
+      <c r="S64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D65" s="2"/>
+      <c r="E65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="P65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R65" s="2"/>
+      <c r="S65" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D66" s="2"/>
+      <c r="E66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R66" s="2"/>
+      <c r="S66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK66" t="s" s="2">
         <v>104</v>
       </c>
     </row>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.23.5</t>
+    <t>2.24.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="158">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.24.0</t>
+    <t>2.19.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -405,24 +405,6 @@
     <t>Limit responses of CarePlan to match the author of the given SOR-code.</t>
   </si>
   <si>
-    <t>VSLatest</t>
-  </si>
-  <si>
-    <t>https://kip.rkkp.dk/fhir/StructureDefinition/VSLatest</t>
-  </si>
-  <si>
-    <t>SearchParameterValueSetLatest</t>
-  </si>
-  <si>
-    <t>Search Parameter - Latest for ValueSets</t>
-  </si>
-  <si>
-    <t>2026-07-09T00:00:00+02:00</t>
-  </si>
-  <si>
-    <t>Limit response of ValueSets to match given Latest.</t>
-  </si>
-  <si>
     <t>access-sor-code</t>
   </si>
   <si>
@@ -454,31 +436,6 @@
   </si>
   <si>
     <t>Limit response of Patient to match given CPR.</t>
-  </si>
-  <si>
-    <t>plan-definition-action-display-order</t>
-  </si>
-  <si>
-    <t>https://kip.rkkp.dk/fhir/StructureDefinition/plan-definition-action-display-order</t>
-  </si>
-  <si>
-    <t>PlanDefinitionActionDisplayOrder</t>
-  </si>
-  <si>
-    <t>Display Order for PlanDefinition Action</t>
-  </si>
-  <si>
-    <t>2026-03-24T00:00:00+02:00</t>
-  </si>
-  <si>
-    <t>Specifies the desired display order of a PlanDefinition action (e.g. Questionnaire references). Lower values are displayed first.</t>
-  </si>
-  <si>
-    <t>element:PlanDefinition.action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">integer
-</t>
   </si>
   <si>
     <t>questionnaire-response-reference</t>
@@ -672,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B286"/>
+  <dimension ref="A1:B242"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1766,7 +1723,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="142">
@@ -1798,7 +1755,7 @@
         <v>23</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="146">
@@ -1882,7 +1839,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="157">
@@ -1890,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="158">
@@ -1906,7 +1863,7 @@
         <v>8</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="160">
@@ -1914,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="161">
@@ -1936,7 +1893,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="164">
@@ -1968,7 +1925,7 @@
         <v>23</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="168">
@@ -2052,7 +2009,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="179">
@@ -2060,7 +2017,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="180">
@@ -2076,7 +2033,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="182">
@@ -2084,7 +2041,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="183">
@@ -2106,7 +2063,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>148</v>
+        <v>131</v>
       </c>
     </row>
     <row r="186">
@@ -2138,7 +2095,7 @@
         <v>23</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="190">
@@ -2206,7 +2163,7 @@
         <v>39</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>150</v>
+        <v>40</v>
       </c>
     </row>
     <row r="199">
@@ -2222,7 +2179,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="201">
@@ -2230,7 +2187,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="202">
@@ -2246,7 +2203,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="204">
@@ -2254,7 +2211,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="205">
@@ -2276,7 +2233,7 @@
         <v>15</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="208">
@@ -2308,7 +2265,7 @@
         <v>23</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="212">
@@ -2392,7 +2349,7 @@
         <v>2</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="223">
@@ -2400,7 +2357,7 @@
         <v>4</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="224">
@@ -2416,7 +2373,7 @@
         <v>8</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="226">
@@ -2424,7 +2381,7 @@
         <v>10</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="227">
@@ -2446,7 +2403,7 @@
         <v>15</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="230">
@@ -2478,7 +2435,7 @@
         <v>23</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="234">
@@ -2546,346 +2503,6 @@
         <v>39</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B243" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B244" t="s" s="2">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B245" t="s" s="2">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B246" t="s" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B247" t="s" s="2">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B248" t="s" s="2">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B249" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B250" s="2"/>
-    </row>
-    <row r="251">
-      <c r="A251" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B251" t="s" s="2">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B252" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B253" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B254" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B255" t="s" s="2">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B256" s="2"/>
-    </row>
-    <row r="257">
-      <c r="A257" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B257" s="2"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B258" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B259" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B260" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B261" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B262" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B263" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B264" t="s" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B265" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B266" t="s" s="2">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B267" t="s" s="2">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B268" t="s" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B269" t="s" s="2">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B270" t="s" s="2">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B271" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B272" s="2"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B273" t="s" s="2">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B274" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B275" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B276" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B277" t="s" s="2">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B278" s="2"/>
-    </row>
-    <row r="279">
-      <c r="A279" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B279" s="2"/>
-    </row>
-    <row r="280">
-      <c r="A280" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B280" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="B281" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B282" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B283" t="s" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B284" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B285" t="s" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B286" t="s" s="2">
         <v>40</v>
       </c>
     </row>
@@ -2896,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK66"/>
+  <dimension ref="A1:AK56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.04296875" customWidth="true" bestFit="true"/>
@@ -6079,7 +5696,7 @@
         <v>22</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>102</v>
@@ -6188,7 +5805,7 @@
         <v>136</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -6670,7 +6287,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>32</v>
@@ -6702,10 +6319,10 @@
         <v>79</v>
       </c>
       <c r="M37" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>143</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -6773,7 +6390,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>82</v>
@@ -6876,7 +6493,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>88</v>
@@ -6979,7 +6596,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>95</v>
@@ -7025,7 +6642,7 @@
       </c>
       <c r="R40" s="2"/>
       <c r="S40" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>22</v>
@@ -7084,7 +6701,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>100</v>
@@ -7187,7 +6804,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>32</v>
@@ -7219,10 +6836,10 @@
         <v>79</v>
       </c>
       <c r="M42" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>149</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -7290,7 +6907,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>82</v>
@@ -7393,7 +7010,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>88</v>
@@ -7496,7 +7113,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>95</v>
@@ -7542,7 +7159,7 @@
       </c>
       <c r="R45" s="2"/>
       <c r="S45" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>22</v>
@@ -7601,7 +7218,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>100</v>
@@ -7630,7 +7247,7 @@
         <v>22</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>151</v>
+        <v>84</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>102</v>
@@ -7704,7 +7321,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>32</v>
@@ -7736,10 +7353,10 @@
         <v>79</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -7807,7 +7424,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>82</v>
@@ -7910,7 +7527,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>88</v>
@@ -8013,7 +7630,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>95</v>
@@ -8059,7 +7676,7 @@
       </c>
       <c r="R50" s="2"/>
       <c r="S50" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>22</v>
@@ -8118,7 +7735,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>100</v>
@@ -8221,7 +7838,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>32</v>
@@ -8253,10 +7870,10 @@
         <v>79</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -8324,7 +7941,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>82</v>
@@ -8427,7 +8044,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>88</v>
@@ -8530,7 +8147,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>95</v>
@@ -8576,7 +8193,7 @@
       </c>
       <c r="R55" s="2"/>
       <c r="S55" t="s" s="2">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>22</v>
@@ -8635,7 +8252,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>100</v>
@@ -8733,1040 +8350,6 @@
         <v>22</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D57" s="2"/>
-      <c r="E57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F57" s="2"/>
-      <c r="G57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="O57" s="2"/>
-      <c r="P57" s="2"/>
-      <c r="Q57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R57" s="2"/>
-      <c r="S57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="C58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="D58" s="2"/>
-      <c r="E58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F58" s="2"/>
-      <c r="G58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
-      <c r="Q58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R58" s="2"/>
-      <c r="S58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="D59" s="2"/>
-      <c r="E59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F59" s="2"/>
-      <c r="G59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="O59" s="2"/>
-      <c r="P59" s="2"/>
-      <c r="Q59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R59" s="2"/>
-      <c r="S59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="D60" s="2"/>
-      <c r="E60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F60" s="2"/>
-      <c r="G60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="P60" s="2"/>
-      <c r="Q60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R60" s="2"/>
-      <c r="S60" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="D61" s="2"/>
-      <c r="E61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F61" s="2"/>
-      <c r="G61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" s="2"/>
-      <c r="Q61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R61" s="2"/>
-      <c r="S61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D62" s="2"/>
-      <c r="E62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F62" s="2"/>
-      <c r="G62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" s="2"/>
-      <c r="Q62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R62" s="2"/>
-      <c r="S62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="D63" s="2"/>
-      <c r="E63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F63" s="2"/>
-      <c r="G63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" s="2"/>
-      <c r="Q63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R63" s="2"/>
-      <c r="S63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="D64" s="2"/>
-      <c r="E64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F64" s="2"/>
-      <c r="G64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="O64" s="2"/>
-      <c r="P64" s="2"/>
-      <c r="Q64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R64" s="2"/>
-      <c r="S64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="D65" s="2"/>
-      <c r="E65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F65" s="2"/>
-      <c r="G65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="P65" s="2"/>
-      <c r="Q65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R65" s="2"/>
-      <c r="S65" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="D66" s="2"/>
-      <c r="E66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="F66" s="2"/>
-      <c r="G66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="O66" s="2"/>
-      <c r="P66" s="2"/>
-      <c r="Q66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="R66" s="2"/>
-      <c r="S66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="AK66" t="s" s="2">
         <v>104</v>
       </c>
     </row>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2294" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2698" uniqueCount="172">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.19.5</t>
+    <t>2.25.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -405,6 +405,24 @@
     <t>Limit responses of CarePlan to match the author of the given SOR-code.</t>
   </si>
   <si>
+    <t>VSLatest</t>
+  </si>
+  <si>
+    <t>https://kip.rkkp.dk/fhir/StructureDefinition/VSLatest</t>
+  </si>
+  <si>
+    <t>SearchParameterValueSetLatest</t>
+  </si>
+  <si>
+    <t>Search Parameter - Latest for ValueSets</t>
+  </si>
+  <si>
+    <t>2026-07-09T00:00:00+02:00</t>
+  </si>
+  <si>
+    <t>Limit response of ValueSets to match given Latest.</t>
+  </si>
+  <si>
     <t>access-sor-code</t>
   </si>
   <si>
@@ -436,6 +454,31 @@
   </si>
   <si>
     <t>Limit response of Patient to match given CPR.</t>
+  </si>
+  <si>
+    <t>plan-definition-action-display-order</t>
+  </si>
+  <si>
+    <t>https://kip.rkkp.dk/fhir/StructureDefinition/plan-definition-action-display-order</t>
+  </si>
+  <si>
+    <t>PlanDefinitionActionDisplayOrder</t>
+  </si>
+  <si>
+    <t>Display Order for PlanDefinition Action</t>
+  </si>
+  <si>
+    <t>2026-03-24T00:00:00+02:00</t>
+  </si>
+  <si>
+    <t>Specifies the desired display order of a PlanDefinition action (e.g. Questionnaire references). Lower values are displayed first.</t>
+  </si>
+  <si>
+    <t>element:PlanDefinition.action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">integer
+</t>
   </si>
   <si>
     <t>questionnaire-response-reference</t>
@@ -629,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B242"/>
+  <dimension ref="A1:B286"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1723,7 +1766,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="142">
@@ -1755,7 +1798,7 @@
         <v>23</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="146">
@@ -1839,7 +1882,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="157">
@@ -1847,7 +1890,7 @@
         <v>4</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="158">
@@ -1863,7 +1906,7 @@
         <v>8</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="160">
@@ -1871,7 +1914,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="161">
@@ -1893,7 +1936,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="164">
@@ -1925,7 +1968,7 @@
         <v>23</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="168">
@@ -2009,7 +2052,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="179">
@@ -2017,7 +2060,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="180">
@@ -2033,7 +2076,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="182">
@@ -2041,7 +2084,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="183">
@@ -2063,7 +2106,7 @@
         <v>15</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="186">
@@ -2095,7 +2138,7 @@
         <v>23</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="190">
@@ -2163,7 +2206,7 @@
         <v>39</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>40</v>
+        <v>150</v>
       </c>
     </row>
     <row r="199">
@@ -2179,7 +2222,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="201">
@@ -2187,7 +2230,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="202">
@@ -2203,7 +2246,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="204">
@@ -2211,7 +2254,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="205">
@@ -2233,7 +2276,7 @@
         <v>15</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="208">
@@ -2265,7 +2308,7 @@
         <v>23</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="212">
@@ -2349,7 +2392,7 @@
         <v>2</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="223">
@@ -2357,7 +2400,7 @@
         <v>4</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="224">
@@ -2373,7 +2416,7 @@
         <v>8</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="226">
@@ -2381,7 +2424,7 @@
         <v>10</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="227">
@@ -2403,7 +2446,7 @@
         <v>15</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="230">
@@ -2435,7 +2478,7 @@
         <v>23</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="234">
@@ -2503,6 +2546,346 @@
         <v>39</v>
       </c>
       <c r="B242" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B243" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B250" s="2"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B256" s="2"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B257" s="2"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B265" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>8</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B272" s="2"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B278" s="2"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B279" s="2"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B280" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B286" t="s" s="2">
         <v>40</v>
       </c>
     </row>
@@ -2513,7 +2896,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK56"/>
+  <dimension ref="A1:AK66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.04296875" customWidth="true" bestFit="true"/>
@@ -5696,7 +6079,7 @@
         <v>22</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="M31" t="s" s="2">
         <v>102</v>
@@ -5805,7 +6188,7 @@
         <v>136</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
@@ -6287,7 +6670,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>32</v>
@@ -6319,10 +6702,10 @@
         <v>79</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
@@ -6390,7 +6773,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>82</v>
@@ -6493,7 +6876,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>88</v>
@@ -6596,7 +6979,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>95</v>
@@ -6642,7 +7025,7 @@
       </c>
       <c r="R40" s="2"/>
       <c r="S40" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>22</v>
@@ -6701,7 +7084,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>100</v>
@@ -6804,7 +7187,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>32</v>
@@ -6836,10 +7219,10 @@
         <v>79</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" s="2"/>
@@ -6907,7 +7290,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>82</v>
@@ -7010,7 +7393,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>88</v>
@@ -7113,7 +7496,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>95</v>
@@ -7159,7 +7542,7 @@
       </c>
       <c r="R45" s="2"/>
       <c r="S45" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>22</v>
@@ -7218,7 +7601,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>100</v>
@@ -7247,7 +7630,7 @@
         <v>22</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>102</v>
@@ -7321,7 +7704,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>32</v>
@@ -7353,10 +7736,10 @@
         <v>79</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" s="2"/>
@@ -7424,7 +7807,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>82</v>
@@ -7527,7 +7910,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>88</v>
@@ -7630,7 +8013,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>95</v>
@@ -7676,7 +8059,7 @@
       </c>
       <c r="R50" s="2"/>
       <c r="S50" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>22</v>
@@ -7735,7 +8118,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>100</v>
@@ -7838,7 +8221,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>32</v>
@@ -7870,10 +8253,10 @@
         <v>79</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" s="2"/>
@@ -7941,7 +8324,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>82</v>
@@ -8044,7 +8427,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>88</v>
@@ -8147,7 +8530,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>95</v>
@@ -8193,7 +8576,7 @@
       </c>
       <c r="R55" s="2"/>
       <c r="S55" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>22</v>
@@ -8252,7 +8635,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>100</v>
@@ -8350,6 +8733,1040 @@
         <v>22</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F57" s="2"/>
+      <c r="G57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R57" s="2"/>
+      <c r="S57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="D58" s="2"/>
+      <c r="E58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F58" s="2"/>
+      <c r="G58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R58" s="2"/>
+      <c r="S58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="D59" s="2"/>
+      <c r="E59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R59" s="2"/>
+      <c r="S59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F60" s="2"/>
+      <c r="G60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="P60" s="2"/>
+      <c r="Q60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R60" s="2"/>
+      <c r="S60" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D61" s="2"/>
+      <c r="E61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F61" s="2"/>
+      <c r="G61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R61" s="2"/>
+      <c r="S61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D62" s="2"/>
+      <c r="E62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F62" s="2"/>
+      <c r="G62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R62" s="2"/>
+      <c r="S62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="D63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F63" s="2"/>
+      <c r="G63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R63" s="2"/>
+      <c r="S63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="D64" s="2"/>
+      <c r="E64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F64" s="2"/>
+      <c r="G64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R64" s="2"/>
+      <c r="S64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D65" s="2"/>
+      <c r="E65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F65" s="2"/>
+      <c r="G65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="P65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R65" s="2"/>
+      <c r="S65" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D66" s="2"/>
+      <c r="E66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="R66" s="2"/>
+      <c r="S66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="AK66" t="s" s="2">
         <v>104</v>
       </c>
     </row>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.25.0</t>
+    <t>1.25.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/all-profiles.xlsx
+++ b/fhir/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.25.1</t>
+    <t>2.26.0</t>
   </si>
   <si>
     <t>Name</t>
